--- a/Excel/StoneSetConfig.xlsx
+++ b/Excel/StoneSetConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>#</t>
   </si>
@@ -35,9 +35,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -80,10 +77,10 @@
     <t>手镯</t>
   </si>
   <si>
+    <t>2,3</t>
+  </si>
+  <si>
     <t>戒指</t>
-  </si>
-  <si>
-    <t>2,3</t>
   </si>
   <si>
     <t>腰带</t>
@@ -1057,28 +1054,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="12.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.25" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="9:9">
-      <c r="I1" s="1" t="s">
+    <row r="1" customHeight="1" spans="8:8">
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="9:9">
-      <c r="I2" s="1" t="s">
+    <row r="2" customHeight="1" spans="8:8">
+      <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1088,13 +1085,10 @@
       <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:8">
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1104,15 +1098,12 @@
       <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
+      <c r="C5" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:8">
-      <c r="C5" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>5</v>
@@ -1120,386 +1111,348 @@
       <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>7</v>
-      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="L6" s="4"/>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="2">
         <v>2</v>
       </c>
-      <c r="D7" s="2">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>11</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="L7" s="4"/>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="4"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:12">
+      <c r="J8" s="2"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="4"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="J9" s="2"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="2">
-        <v>3</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="4"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="J10" s="2"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="2">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" customHeight="1" spans="3:12">
+      <c r="J11" s="2"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="3:11">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="E12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="4"/>
-    </row>
-    <row r="13" customHeight="1" spans="3:12">
+      <c r="J12" s="2"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="13" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F13" s="5" t="s">
-        <v>18</v>
-      </c>
+      <c r="E13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="4"/>
-    </row>
-    <row r="14" customHeight="1" spans="3:12">
+      <c r="J13" s="2"/>
+      <c r="K13" s="4"/>
+    </row>
+    <row r="14" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="D14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="4"/>
-    </row>
-    <row r="15" customHeight="1" spans="3:12">
+      <c r="J14" s="2"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" customHeight="1" spans="3:11">
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="2">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="D15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="4"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:12">
+      <c r="J15" s="2"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:11">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="4"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="5:12">
-      <c r="E17" s="1"/>
-      <c r="L17" s="4"/>
-    </row>
-    <row r="18" customHeight="1" spans="1:12">
+      <c r="J16" s="2"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:11">
+      <c r="D17" s="1"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="4"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="5:12">
-      <c r="E19" s="1"/>
-      <c r="L19" s="4"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="5:12">
-      <c r="E20" s="1"/>
-      <c r="L20" s="4"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="J18" s="2"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="4:11">
+      <c r="D19" s="1"/>
+      <c r="K19" s="4"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="4:11">
+      <c r="D20" s="1"/>
+      <c r="K20" s="4"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="4"/>
-    </row>
-    <row r="22" customHeight="1" spans="1:12">
+      <c r="J21" s="2"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="4"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="5:12">
+      <c r="J22" s="2"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="4:11">
+      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="L23" s="4"/>
-    </row>
-    <row r="24" customHeight="1" spans="1:12">
+      <c r="K23" s="4"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="4"/>
-    </row>
-    <row r="25" customHeight="1" spans="11:12">
-      <c r="K25" s="2"/>
-      <c r="L25" s="4"/>
-    </row>
-    <row r="26" customHeight="1" spans="11:12">
-      <c r="K26" s="2"/>
-      <c r="L26" s="4"/>
-    </row>
-    <row r="27" customHeight="1" spans="11:12">
-      <c r="K27" s="2"/>
-      <c r="L27" s="4"/>
-    </row>
-    <row r="28" customHeight="1" spans="11:12">
-      <c r="K28" s="2"/>
-      <c r="L28" s="4"/>
-    </row>
-    <row r="29" customHeight="1" spans="11:12">
-      <c r="K29" s="2"/>
-      <c r="L29" s="4"/>
-    </row>
-    <row r="30" customHeight="1" spans="11:12">
-      <c r="K30" s="2"/>
-      <c r="L30" s="4"/>
-    </row>
-    <row r="31" customHeight="1" spans="11:12">
-      <c r="K31" s="2"/>
-      <c r="L31" s="4"/>
-    </row>
-    <row r="32" customHeight="1" spans="11:12">
-      <c r="K32" s="2"/>
-      <c r="L32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="11:12">
-      <c r="K33" s="2"/>
-      <c r="L33" s="4"/>
-    </row>
-    <row r="34" customHeight="1" spans="11:12">
-      <c r="K34" s="2"/>
-      <c r="L34" s="4"/>
-    </row>
-    <row r="35" customHeight="1" spans="11:12">
-      <c r="K35" s="2"/>
-      <c r="L35" s="4"/>
-    </row>
-    <row r="36" customHeight="1" spans="11:12">
-      <c r="K36" s="2"/>
-      <c r="L36" s="4"/>
-    </row>
-    <row r="37" customHeight="1" spans="11:12">
-      <c r="K37" s="2"/>
-      <c r="L37" s="4"/>
-    </row>
-    <row r="38" customHeight="1" spans="11:12">
-      <c r="K38" s="2"/>
-      <c r="L38" s="4"/>
-    </row>
-    <row r="39" customHeight="1" spans="11:12">
-      <c r="K39" s="2"/>
-      <c r="L39" s="4"/>
-    </row>
-    <row r="40" customHeight="1" spans="11:12">
-      <c r="K40" s="2"/>
-      <c r="L40" s="4"/>
-    </row>
-    <row r="41" customHeight="1" spans="11:12">
-      <c r="K41" s="2"/>
-      <c r="L41" s="4"/>
-    </row>
-    <row r="42" customHeight="1" spans="11:12">
-      <c r="K42" s="2"/>
-      <c r="L42" s="4"/>
-    </row>
-    <row r="43" customHeight="1" spans="11:12">
-      <c r="K43" s="2"/>
-      <c r="L43" s="4"/>
-    </row>
-    <row r="44" customHeight="1" spans="11:12">
-      <c r="K44" s="2"/>
-      <c r="L44" s="4"/>
-    </row>
-    <row r="45" customHeight="1" spans="11:12">
-      <c r="K45" s="2"/>
-      <c r="L45" s="4"/>
-    </row>
-    <row r="46" customHeight="1" spans="11:12">
-      <c r="K46" s="2"/>
-      <c r="L46" s="4"/>
-    </row>
-    <row r="47" customHeight="1" spans="11:12">
-      <c r="K47" s="2"/>
-      <c r="L47" s="4"/>
-    </row>
-    <row r="48" customHeight="1" spans="11:12">
-      <c r="K48" s="2"/>
-      <c r="L48" s="4"/>
-    </row>
-    <row r="49" customHeight="1" spans="11:12">
-      <c r="K49" s="2"/>
-      <c r="L49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="11:12">
-      <c r="K50" s="2"/>
-      <c r="L50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="11:12">
-      <c r="K51" s="2"/>
-      <c r="L51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="11:12">
-      <c r="K52" s="2"/>
-      <c r="L52" s="4"/>
-    </row>
-    <row r="53" customHeight="1" spans="11:12">
-      <c r="K53" s="2"/>
-      <c r="L53" s="4"/>
-    </row>
-    <row r="54" customHeight="1" spans="11:12">
-      <c r="K54" s="2"/>
-      <c r="L54" s="4"/>
-    </row>
-    <row r="55" customHeight="1" spans="11:12">
-      <c r="K55" s="2"/>
-      <c r="L55" s="4"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="4"/>
+    </row>
+    <row r="25" customHeight="1" spans="10:11">
+      <c r="J25" s="2"/>
+      <c r="K25" s="4"/>
+    </row>
+    <row r="26" customHeight="1" spans="10:11">
+      <c r="J26" s="2"/>
+      <c r="K26" s="4"/>
+    </row>
+    <row r="27" customHeight="1" spans="10:11">
+      <c r="J27" s="2"/>
+      <c r="K27" s="4"/>
+    </row>
+    <row r="28" customHeight="1" spans="10:11">
+      <c r="J28" s="2"/>
+      <c r="K28" s="4"/>
+    </row>
+    <row r="29" customHeight="1" spans="10:11">
+      <c r="J29" s="2"/>
+      <c r="K29" s="4"/>
+    </row>
+    <row r="30" customHeight="1" spans="10:11">
+      <c r="J30" s="2"/>
+      <c r="K30" s="4"/>
+    </row>
+    <row r="31" customHeight="1" spans="10:11">
+      <c r="J31" s="2"/>
+      <c r="K31" s="4"/>
+    </row>
+    <row r="32" customHeight="1" spans="10:11">
+      <c r="J32" s="2"/>
+      <c r="K32" s="4"/>
+    </row>
+    <row r="33" customHeight="1" spans="10:11">
+      <c r="J33" s="2"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" customHeight="1" spans="10:11">
+      <c r="J34" s="2"/>
+      <c r="K34" s="4"/>
+    </row>
+    <row r="35" customHeight="1" spans="10:11">
+      <c r="J35" s="2"/>
+      <c r="K35" s="4"/>
+    </row>
+    <row r="36" customHeight="1" spans="10:11">
+      <c r="J36" s="2"/>
+      <c r="K36" s="4"/>
+    </row>
+    <row r="37" customHeight="1" spans="10:11">
+      <c r="J37" s="2"/>
+      <c r="K37" s="4"/>
+    </row>
+    <row r="38" customHeight="1" spans="10:11">
+      <c r="J38" s="2"/>
+      <c r="K38" s="4"/>
+    </row>
+    <row r="39" customHeight="1" spans="10:11">
+      <c r="J39" s="2"/>
+      <c r="K39" s="4"/>
+    </row>
+    <row r="40" customHeight="1" spans="10:11">
+      <c r="J40" s="2"/>
+      <c r="K40" s="4"/>
+    </row>
+    <row r="41" customHeight="1" spans="10:11">
+      <c r="J41" s="2"/>
+      <c r="K41" s="4"/>
+    </row>
+    <row r="42" customHeight="1" spans="10:11">
+      <c r="J42" s="2"/>
+      <c r="K42" s="4"/>
+    </row>
+    <row r="43" customHeight="1" spans="10:11">
+      <c r="J43" s="2"/>
+      <c r="K43" s="4"/>
+    </row>
+    <row r="44" customHeight="1" spans="10:11">
+      <c r="J44" s="2"/>
+      <c r="K44" s="4"/>
+    </row>
+    <row r="45" customHeight="1" spans="10:11">
+      <c r="J45" s="2"/>
+      <c r="K45" s="4"/>
+    </row>
+    <row r="46" customHeight="1" spans="10:11">
+      <c r="J46" s="2"/>
+      <c r="K46" s="4"/>
+    </row>
+    <row r="47" customHeight="1" spans="10:11">
+      <c r="J47" s="2"/>
+      <c r="K47" s="4"/>
+    </row>
+    <row r="48" customHeight="1" spans="10:11">
+      <c r="J48" s="2"/>
+      <c r="K48" s="4"/>
+    </row>
+    <row r="49" customHeight="1" spans="10:11">
+      <c r="J49" s="2"/>
+      <c r="K49" s="4"/>
+    </row>
+    <row r="50" customHeight="1" spans="10:11">
+      <c r="J50" s="2"/>
+      <c r="K50" s="4"/>
+    </row>
+    <row r="51" customHeight="1" spans="10:11">
+      <c r="J51" s="2"/>
+      <c r="K51" s="4"/>
+    </row>
+    <row r="52" customHeight="1" spans="10:11">
+      <c r="J52" s="2"/>
+      <c r="K52" s="4"/>
+    </row>
+    <row r="53" customHeight="1" spans="10:11">
+      <c r="J53" s="2"/>
+      <c r="K53" s="4"/>
+    </row>
+    <row r="54" customHeight="1" spans="10:11">
+      <c r="J54" s="2"/>
+      <c r="K54" s="4"/>
+    </row>
+    <row r="55" customHeight="1" spans="10:11">
+      <c r="J55" s="2"/>
+      <c r="K55" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 D3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/StoneSetConfig.xlsx
+++ b/Excel/StoneSetConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -87,6 +87,21 @@
   </si>
   <si>
     <t>鞋子</t>
+  </si>
+  <si>
+    <t>11,13,14</t>
+  </si>
+  <si>
+    <t>12,14</t>
+  </si>
+  <si>
+    <t>11,12,13,14</t>
+  </si>
+  <si>
+    <t>11,12,14</t>
+  </si>
+  <si>
+    <t>12,13,14</t>
   </si>
 </sst>
 </file>
@@ -1065,17 +1080,17 @@
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="8:8">
+    <row r="1" customHeight="1" spans="3:11">
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="8:8">
+    <row r="2" customHeight="1" spans="3:11">
       <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1088,7 +1103,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1101,7 +1116,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:7">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1271,33 +1286,71 @@
       <c r="J16" s="2"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="4:11">
-      <c r="D17" s="1"/>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C17" s="2">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="K17" s="4"/>
     </row>
     <row r="18" customHeight="1" spans="1:11">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="C18" s="2">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="4:11">
-      <c r="D19" s="1"/>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C19" s="2">
+        <v>13</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="K19" s="4"/>
     </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="4:11">
-      <c r="D20" s="1"/>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C20" s="2">
+        <v>14</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="K20" s="4"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:11">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="C21" s="2">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="J21" s="2"/>
@@ -1306,13 +1359,28 @@
     <row r="22" customHeight="1" spans="1:11">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="J22" s="2"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="4:11">
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:11">
+      <c r="C23" s="2">
+        <v>17</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1322,39 +1390,65 @@
     <row r="24" customHeight="1" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
+      <c r="C24" s="2">
+        <v>18</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="J24" s="2"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" customHeight="1" spans="10:11">
+    <row r="25" customHeight="1" spans="1:11">
+      <c r="C25" s="2">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" customHeight="1" spans="10:11">
+    <row r="26" customHeight="1" spans="1:11">
+      <c r="C26" s="2">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="J26" s="2"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" customHeight="1" spans="10:11">
+    <row r="27" customHeight="1" spans="1:11">
       <c r="J27" s="2"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" customHeight="1" spans="10:11">
+    <row r="28" customHeight="1" spans="1:11">
       <c r="J28" s="2"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" customHeight="1" spans="10:11">
+    <row r="29" customHeight="1" spans="1:11">
       <c r="J29" s="2"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" customHeight="1" spans="10:11">
+    <row r="30" customHeight="1" spans="1:11">
       <c r="J30" s="2"/>
       <c r="K30" s="4"/>
     </row>
-    <row r="31" customHeight="1" spans="10:11">
+    <row r="31" customHeight="1" spans="1:11">
       <c r="J31" s="2"/>
       <c r="K31" s="4"/>
     </row>
-    <row r="32" customHeight="1" spans="10:11">
+    <row r="32" customHeight="1" spans="1:11">
       <c r="J32" s="2"/>
       <c r="K32" s="4"/>
     </row>
@@ -1452,7 +1546,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 D3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/StoneSetConfig.xlsx
+++ b/Excel/StoneSetConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>#</t>
   </si>
@@ -89,19 +89,43 @@
     <t>鞋子</t>
   </si>
   <si>
+    <t>极武器</t>
+  </si>
+  <si>
     <t>11,13,14</t>
   </si>
   <si>
+    <t>极衣服</t>
+  </si>
+  <si>
     <t>12,14</t>
   </si>
   <si>
+    <t>极项链</t>
+  </si>
+  <si>
     <t>11,12,13,14</t>
   </si>
   <si>
+    <t>极头盔</t>
+  </si>
+  <si>
     <t>11,12,14</t>
   </si>
   <si>
+    <t>极手镯</t>
+  </si>
+  <si>
     <t>12,13,14</t>
+  </si>
+  <si>
+    <t>极戒指</t>
+  </si>
+  <si>
+    <t>极腰带</t>
+  </si>
+  <si>
+    <t>极鞋子</t>
   </si>
 </sst>
 </file>
@@ -1291,10 +1315,10 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" s="4"/>
     </row>
@@ -1305,10 +1329,10 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -1320,10 +1344,10 @@
         <v>13</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K19" s="4"/>
     </row>
@@ -1332,10 +1356,10 @@
         <v>14</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K20" s="4"/>
     </row>
@@ -1346,10 +1370,10 @@
         <v>15</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1363,10 +1387,10 @@
         <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="4"/>
@@ -1376,10 +1400,10 @@
         <v>17</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1394,10 +1418,10 @@
         <v>18</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="4"/>
@@ -1407,10 +1431,10 @@
         <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="4"/>
@@ -1420,10 +1444,10 @@
         <v>20</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J26" s="2"/>
       <c r="K26" s="4"/>
